--- a/QlikSyncPro_Inputs.xlsx
+++ b/QlikSyncPro_Inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DYY\Downloads\lb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://qliktechnologies365-my.sharepoint.com/personal/dyy_qlik_com/Documents/QS Pro For Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6968D161-B95F-4787-8E5F-8B27278C5973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{961C5A99-C1C8-422B-8581-6B5CBAF8B984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8673BB4F-D374-4918-998C-80FB1D4FD26D}"/>
   <bookViews>
-    <workbookView xWindow="7755" yWindow="765" windowWidth="16500" windowHeight="14505" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8" yWindow="667" windowWidth="21480" windowHeight="12263" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="spaces" sheetId="3" r:id="rId1"/>
@@ -44,54 +44,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="119">
+  <si>
+    <t>spacename</t>
+  </si>
+  <si>
+    <t>spacetype</t>
+  </si>
+  <si>
+    <t>spaceowner</t>
+  </si>
+  <si>
+    <t>tenant</t>
+  </si>
+  <si>
+    <t>spacedescription</t>
+  </si>
+  <si>
+    <t>newspacename</t>
+  </si>
+  <si>
+    <t>spaceflag</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>managed</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Production spaces for end users, no development possible</t>
+  </si>
+  <si>
+    <t>create</t>
+  </si>
+  <si>
+    <t>Accounting - DEV</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Accounting - UAT</t>
+  </si>
   <si>
     <t>groupname</t>
   </si>
   <si>
-    <t>create</t>
-  </si>
-  <si>
-    <t>shared</t>
-  </si>
-  <si>
     <t>grouprole</t>
   </si>
   <si>
+    <t>grouptype</t>
+  </si>
+  <si>
+    <t>groupdescription</t>
+  </si>
+  <si>
     <t>groupflag</t>
   </si>
   <si>
-    <t>spacename</t>
-  </si>
-  <si>
-    <t>spacetype</t>
-  </si>
-  <si>
-    <t>spaceowner</t>
-  </si>
-  <si>
-    <t>spacedescription</t>
-  </si>
-  <si>
-    <t>spaceflag</t>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>Admin responsible for creating data connections</t>
+  </si>
+  <si>
+    <t>BI team developers crossing all LOBs and builds QVD generation applications</t>
+  </si>
+  <si>
+    <t>LOB codevelopers with access only to QVDs, no data connection access</t>
+  </si>
+  <si>
+    <t>Endusers with only view access, no sheet creation</t>
+  </si>
+  <si>
+    <t>Endusers with permissions to private and community sheets</t>
   </si>
   <si>
     <t>spaceroles</t>
   </si>
   <si>
     <t>spacepermissionsflag</t>
-  </si>
-  <si>
-    <t>newspacename</t>
-  </si>
-  <si>
-    <t>grouptype</t>
-  </si>
-  <si>
-    <t>groupdescription</t>
-  </si>
-  <si>
-    <t>codeveloper</t>
   </si>
   <si>
     <r>
@@ -151,19 +187,34 @@
     </r>
   </si>
   <si>
-    <t>tenant</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>Accounting - DEV</t>
-  </si>
-  <si>
-    <t>custom</t>
-  </si>
-  <si>
-    <t>CSTM_ACCT_CODEV</t>
+    <t>codeveloper</t>
+  </si>
+  <si>
+    <t>facilitator, publisher, dataconsumer</t>
+  </si>
+  <si>
+    <t>consumer</t>
+  </si>
+  <si>
+    <t>contributor</t>
+  </si>
+  <si>
+    <t>facilitator, publisher, dataconsumer, operator</t>
+  </si>
+  <si>
+    <t>dataconsumer</t>
+  </si>
+  <si>
+    <t>facilitator</t>
+  </si>
+  <si>
+    <t>usergroups</t>
+  </si>
+  <si>
+    <t>useremail</t>
+  </si>
+  <si>
+    <t>useremailflag</t>
   </si>
   <si>
     <t>UI Display Name</t>
@@ -172,235 +223,247 @@
     <t>Back-end / API Internal Name</t>
   </si>
   <si>
+    <t>SpaceType</t>
+  </si>
+  <si>
+    <t>UI name</t>
+  </si>
+  <si>
+    <t>API name</t>
+  </si>
+  <si>
+    <t>Role level</t>
+  </si>
+  <si>
+    <t>Permission type</t>
+  </si>
+  <si>
     <t>Can manage</t>
   </si>
   <si>
-    <t>facilitator</t>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Analytics Admin</t>
+  </si>
+  <si>
+    <t>AnalyticsAdmin</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Permissive</t>
   </si>
   <si>
     <t>Can edit</t>
   </si>
   <si>
+    <t>producer</t>
+  </si>
+  <si>
+    <t>Shared</t>
+  </si>
+  <si>
+    <t>Audit Admin</t>
+  </si>
+  <si>
+    <t>AuditAdmin</t>
+  </si>
+  <si>
     <t>Can edit data in applications</t>
   </si>
   <si>
+    <t>Automation Creator</t>
+  </si>
+  <si>
+    <t>AutomationCreator</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
     <t>Can view</t>
   </si>
   <si>
+    <t>Automl Deployment Contributor</t>
+  </si>
+  <si>
+    <t>AutomlDeploymentContributor</t>
+  </si>
+  <si>
+    <t>Can contribute</t>
+  </si>
+  <si>
+    <t>Managed</t>
+  </si>
+  <si>
+    <t>Automl Experiment Contributor</t>
+  </si>
+  <si>
+    <t>AutomlExperimentContributor</t>
+  </si>
+  <si>
     <t>Can consume data</t>
   </si>
   <si>
-    <t>dataconsumer</t>
+    <t>Collaboration Platform User</t>
+  </si>
+  <si>
+    <t>CollaborationPlatformUser</t>
+  </si>
+  <si>
+    <t>Can publish</t>
   </si>
   <si>
     <t>publisher</t>
   </si>
   <si>
+    <t>Data Admin</t>
+  </si>
+  <si>
+    <t>DataAdmin</t>
+  </si>
+  <si>
     <t>Can operate</t>
   </si>
   <si>
     <t>operator</t>
   </si>
   <si>
+    <t>Data Product Manager</t>
+  </si>
+  <si>
+    <t>DataProductManager</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
     <t>owner</t>
   </si>
   <si>
-    <t>Both</t>
-  </si>
-  <si>
-    <t>Shared</t>
-  </si>
-  <si>
-    <t>Managed</t>
-  </si>
-  <si>
-    <t>Can publish</t>
+    <t>Data Services Contributor</t>
+  </si>
+  <si>
+    <t>DataServicesContributor</t>
+  </si>
+  <si>
+    <t>Has restricted view</t>
+  </si>
+  <si>
+    <t>basicconsumer</t>
+  </si>
+  <si>
+    <t>Data Space Creator</t>
+  </si>
+  <si>
+    <t>DataSpaceCreator</t>
+  </si>
+  <si>
+    <t>Can view data</t>
+  </si>
+  <si>
+    <t>datapreview</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Embedded Analytics User</t>
+  </si>
+  <si>
+    <t>EmbeddedAnalyticsUser</t>
+  </si>
+  <si>
+    <t>Restrictive</t>
+  </si>
+  <si>
+    <t>Managed Space Creator</t>
+  </si>
+  <si>
+    <t>ManagedSpaceCreator</t>
+  </si>
+  <si>
+    <t>Private Analytics Content Creator</t>
+  </si>
+  <si>
+    <t>PrivateAnalyticsContentCreator</t>
+  </si>
+  <si>
+    <t>Shared Space Creator</t>
+  </si>
+  <si>
+    <t>SharedSpaceCreator</t>
+  </si>
+  <si>
+    <t>Steward</t>
+  </si>
+  <si>
+    <t>Tenant Admin</t>
   </si>
   <si>
     <t>TenantAdmin</t>
   </si>
   <si>
-    <t>AnalyticsAdmin</t>
-  </si>
-  <si>
-    <t>DataAdmin</t>
-  </si>
-  <si>
-    <t>Shared Space Creator</t>
-  </si>
-  <si>
-    <t>SharedSpaceCreator</t>
-  </si>
-  <si>
-    <t>Managed Space Creator</t>
-  </si>
-  <si>
-    <t>ManagedSpaceCreator</t>
-  </si>
-  <si>
-    <t>Private Analytics Content Creator</t>
-  </si>
-  <si>
-    <t>PrivateAnalyticsContentCreator</t>
-  </si>
-  <si>
-    <t>Can contribute</t>
-  </si>
-  <si>
-    <t>contributor</t>
-  </si>
-  <si>
-    <t>producer</t>
-  </si>
-  <si>
-    <t>consumer</t>
-  </si>
-  <si>
-    <t>Has restricted view</t>
-  </si>
-  <si>
-    <t>basicconsumer</t>
-  </si>
-  <si>
-    <t>Can view data</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>datapreview</t>
-  </si>
-  <si>
-    <t>UI name</t>
-  </si>
-  <si>
-    <t>API name</t>
-  </si>
-  <si>
-    <t>Role level</t>
-  </si>
-  <si>
-    <t>Permission type</t>
-  </si>
-  <si>
-    <t>Analytics Admin</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>Permissive</t>
-  </si>
-  <si>
-    <t>Audit Admin</t>
-  </si>
-  <si>
-    <t>AuditAdmin</t>
-  </si>
-  <si>
-    <t>Automation Creator</t>
-  </si>
-  <si>
-    <t>AutomationCreator</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Automl Deployment Contributor</t>
-  </si>
-  <si>
-    <t>AutomlDeploymentContributor</t>
-  </si>
-  <si>
-    <t>Automl Experiment Contributor</t>
-  </si>
-  <si>
-    <t>AutomlExperimentContributor</t>
-  </si>
-  <si>
-    <t>Collaboration Platform User</t>
-  </si>
-  <si>
-    <t>CollaborationPlatformUser</t>
-  </si>
-  <si>
-    <t>Data Admin</t>
-  </si>
-  <si>
-    <t>Data Product Manager</t>
-  </si>
-  <si>
-    <t>DataProductManager</t>
-  </si>
-  <si>
-    <t>Data Services Contributor</t>
-  </si>
-  <si>
-    <t>DataServicesContributor</t>
-  </si>
-  <si>
-    <t>Data Space Creator</t>
-  </si>
-  <si>
-    <t>DataSpaceCreator</t>
-  </si>
-  <si>
-    <t>Embedded Analytics User</t>
-  </si>
-  <si>
-    <t>EmbeddedAnalyticsUser</t>
-  </si>
-  <si>
-    <t>Restrictive</t>
-  </si>
-  <si>
-    <t>Steward</t>
-  </si>
-  <si>
-    <t>Tenant Admin</t>
-  </si>
-  <si>
-    <t>SpaceType</t>
-  </si>
-  <si>
-    <t>CSTM_QLIK_ADMIN</t>
-  </si>
-  <si>
-    <t>TenantAdmin, AuditAdmin, API Creator, AutomationCreator</t>
-  </si>
-  <si>
-    <t>LOB developers can codevelop apps</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>usergroups</t>
-  </si>
-  <si>
-    <t>useremail</t>
-  </si>
-  <si>
-    <t>useremailflag</t>
-  </si>
-  <si>
-    <t>remove-value</t>
-  </si>
-  <si>
-    <t>delete</t>
-  </si>
-  <si>
-    <t>Test Space TEMP</t>
+    <t>Custom Groups</t>
+  </si>
+  <si>
+    <t>Same as name of customer group</t>
+  </si>
+  <si>
+    <t>CSTM_ACCOUNTING_CODEV</t>
+  </si>
+  <si>
+    <t>CSTM_ACCOUNTING_USER_CONTRIBUTE</t>
+  </si>
+  <si>
+    <t>CSTM_ACCOUNTING_USER_VIEW</t>
+  </si>
+  <si>
+    <t>CSTM_BUSINESS_INTELLIGENCE_DEVELOPER</t>
+  </si>
+  <si>
+    <t>CSTM_BUSINESS_INTELLIGENCE_AUTOMATION_CREATOR</t>
+  </si>
+  <si>
+    <t>CSTM_BUSINESS_INTELLIGENCE_ADMIN_DC_CREATOR</t>
+  </si>
+  <si>
+    <t>CSTM_ENGINEERING_CODEV</t>
+  </si>
+  <si>
+    <t>CSTM_BUSINESS_INTELLIGENCE_ADMIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSTM_BUSINESS_INTELLIGENCE_ADMIN_PUBLISHER </t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>Development spaces for dev only, no end users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing space </t>
+  </si>
+  <si>
+    <t>TenantAdmin, AuditAdmin, AutomationCreator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutomationCreator </t>
+  </si>
+  <si>
+    <t>ADD EMAILS HERE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#0"/>
+  </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -661,7 +724,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -696,6 +759,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -718,10 +782,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -925,7 +985,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.5703125" style="7" bestFit="1" customWidth="1"/>
@@ -934,342 +994,356 @@
     <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.85546875" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="1"/>
+      <c r="A4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="G4" s="1"/>
+      <c r="D4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11"/>
       <c r="B5" s="1"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11"/>
       <c r="B6" s="1"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11"/>
       <c r="B7" s="1"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
-      <c r="G7" s="1"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11"/>
       <c r="B8" s="1"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="G8" s="1"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
       <c r="B9" s="1"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="G9" s="1"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
       <c r="B10" s="1"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="G11" s="1"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="G12" s="1"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="G20" s="1"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="G21" s="1"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="11"/>
       <c r="B23" s="1"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="G23" s="1"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="11"/>
       <c r="B24" s="1"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11"/>
       <c r="B25" s="1"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
-      <c r="G25" s="1"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="11"/>
       <c r="B26" s="1"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
-      <c r="G26" s="1"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
+      <c r="A27"/>
       <c r="B27" s="1"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
-      <c r="G27" s="1"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
+      <c r="A28"/>
       <c r="B28" s="1"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="B29" s="1"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="G29" s="1"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30"/>
       <c r="B30" s="1"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="G30" s="1"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31"/>
+      <c r="A31" s="2"/>
       <c r="B31" s="1"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="G31" s="1"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32"/>
+      <c r="A32" s="2"/>
       <c r="B32" s="1"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="G32" s="1"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="1"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="1"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="G34" s="1"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
       <c r="B35" s="1"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="G35" s="1"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
       <c r="B36" s="1"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="G36" s="1"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="1"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
-      <c r="G37" s="1"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="1"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="G38" s="1"/>
+      <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="1"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="G39" s="1"/>
+      <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="1"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
-      <c r="G40" s="1"/>
+      <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="1"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="G41" s="1"/>
+      <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="1"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="G42" s="1"/>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="1"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="G43" s="1"/>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="1"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
-      <c r="G44" s="1"/>
+      <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="1"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="1"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="1"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="G47" s="1"/>
+      <c r="G45" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G45" xr:uid="{0ED023FE-C1C7-47E7-B8B9-E86CA85AE201}">
+      <formula1>"create, delete, update"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1277,10 +1351,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568D4303-4E5E-4777-8F67-B9ACCE31E338}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="43" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -1294,138 +1368,190 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="F1" s="5" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
-      <c r="B3" s="2"/>
+      <c r="A3" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="B4" s="10"/>
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="1:6" s="12" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="C5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="A5" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="10"/>
+      <c r="A6" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
+      <c r="A7" s="12" t="s">
+        <v>104</v>
+      </c>
       <c r="B7" s="2"/>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
+      <c r="A8" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11"/>
-    </row>
-    <row r="12" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
-      <c r="B12"/>
-    </row>
-    <row r="13" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13"/>
-    </row>
-    <row r="14" spans="1:6" ht="12" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-    </row>
-    <row r="15" spans="1:6" ht="12" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-    </row>
-    <row r="16" spans="1:6" ht="12" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-    </row>
-    <row r="17" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-    </row>
-    <row r="18" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-    </row>
-    <row r="19" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-    </row>
-    <row r="20" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-    </row>
-    <row r="21" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-    </row>
-    <row r="22" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-    </row>
-    <row r="23" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-    </row>
-    <row r="24" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-    </row>
-    <row r="25" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-    </row>
-    <row r="26" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-    </row>
-    <row r="27" spans="1:1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-    </row>
-    <row r="32" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="12" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="12" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="12" x14ac:dyDescent="0.2">
+      <c r="A11" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F31" xr:uid="{C7BB5AF6-6317-4209-AF60-9494533C345A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F10" xr:uid="{C7BB5AF6-6317-4209-AF60-9494533C345A}">
       <formula1>"create, delete, update"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C31" xr:uid="{8D53CBAD-AAF2-4152-9BBE-C6DB5BD96435}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10" xr:uid="{8D53CBAD-AAF2-4152-9BBE-C6DB5BD96435}">
       <formula1>"idp, custom"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1443,11 +1569,11 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="85.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5703125" style="6" customWidth="1"/>
     <col min="7" max="7" width="56.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="33.140625" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="52" style="6" bestFit="1" customWidth="1"/>
@@ -1455,654 +1581,752 @@
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="3"/>
+      <c r="O1" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="34"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="3"/>
-      <c r="O1" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="33"/>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>91</v>
+      <c r="F2" s="6" t="str">
+        <f>VLOOKUP(B2,groups!A:A,1,FALSE)</f>
+        <v>CSTM_ACCOUNTING_CODEV</v>
       </c>
       <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="A3" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <f>VLOOKUP(B3,groups!A:A,1,FALSE)</f>
+        <v>CSTM_ACCOUNTING_USER_CONTRIBUTE</v>
+      </c>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f>VLOOKUP(B4,groups!A:A,1,FALSE)</f>
+        <v>CSTM_ACCOUNTING_USER_VIEW</v>
+      </c>
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6" t="str">
+        <f>VLOOKUP(B5,groups!A:A,1,FALSE)</f>
+        <v xml:space="preserve">CSTM_BUSINESS_INTELLIGENCE_ADMIN_PUBLISHER </v>
+      </c>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6" t="str">
+        <f>VLOOKUP(B6,groups!A:A,1,FALSE)</f>
+        <v>CSTM_ACCOUNTING_CODEV</v>
+      </c>
       <c r="G6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="6" t="str">
+        <f>VLOOKUP(B7,groups!A:A,1,FALSE)</f>
+        <v>CSTM_BUSINESS_INTELLIGENCE_DEVELOPER</v>
+      </c>
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="A8" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6" t="str">
+        <f>VLOOKUP(B8,groups!A:A,1,FALSE)</f>
+        <v>CSTM_ACCOUNTING_CODEV</v>
+      </c>
       <c r="G8" s="3"/>
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="A9" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="6" t="str">
+        <f>VLOOKUP(B9,groups!A:A,1,FALSE)</f>
+        <v>CSTM_BUSINESS_INTELLIGENCE_DEVELOPER</v>
+      </c>
       <c r="G9" s="3"/>
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="2"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="2"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="2"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="2"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="2"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="12"/>
-      <c r="C16" s="2"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="12"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="12"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="12"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="12"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="12"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="12"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
       <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="12"/>
-      <c r="C23" s="2"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
       <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="12"/>
-      <c r="C24" s="2"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="12"/>
-      <c r="C25" s="2"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
       <c r="D25" s="2"/>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="12"/>
-      <c r="C26" s="2"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="12"/>
-      <c r="C27" s="2"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="12"/>
-      <c r="C28" s="2"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="12"/>
-      <c r="C29" s="2"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="2"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="2"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="2"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
       <c r="D32" s="2"/>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="2"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
       <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="2"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
       <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="2"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="2"/>
+      <c r="A36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
       <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="2"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
       <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="2"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="2"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
       <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="2"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
       <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="11"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="2"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
       <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="2"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
       <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="2"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
       <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="11"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="2"/>
+      <c r="A44" s="32"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
       <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="11"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="2"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
       <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="11"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="2"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="2"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
       <c r="D47" s="2"/>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="2"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
       <c r="D48" s="2"/>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="2"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="2"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
       <c r="D50" s="2"/>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="2"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
       <c r="D51" s="2"/>
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="2"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="11"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="2"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
       <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="2"/>
+      <c r="A54" s="32"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="2"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="2"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="2"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="2"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
       <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="11"/>
-      <c r="C59" s="2"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
       <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="11"/>
-      <c r="C60" s="2"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
       <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="11"/>
-      <c r="C61" s="2"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
       <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="11"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
+      <c r="A62" s="32"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
       <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="11"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
       <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="11"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
+      <c r="A64" s="32"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="11"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
+    <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="32"/>
+      <c r="B65" s="32"/>
+      <c r="C65" s="32"/>
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="12"/>
-      <c r="C66" s="2"/>
+    <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="32"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="12"/>
-      <c r="C67" s="2"/>
+    <row r="67" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="32"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
       <c r="D67" s="2"/>
     </row>
-    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="12"/>
-      <c r="C68" s="2"/>
+    <row r="68" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="32"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="32"/>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="12"/>
-      <c r="C69" s="2"/>
+    <row r="69" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="32"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="32"/>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="2"/>
+    <row r="70" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="32"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="2"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="2"/>
+    <row r="71" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="32"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
+    <row r="72" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="32"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="32"/>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
+    <row r="73" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="32"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="32"/>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
+    <row r="74" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="32"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="32"/>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="2"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="2"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="32"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="32"/>
       <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-    </row>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="2"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="2"/>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="32"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="32"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="2"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="2"/>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="32"/>
+      <c r="B77" s="32"/>
+      <c r="C77" s="32"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="2"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="2"/>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="32"/>
+      <c r="B78" s="32"/>
+      <c r="C78" s="32"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-    </row>
-    <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="2"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="2"/>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="32"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="32"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="2"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="2"/>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="32"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="32"/>
       <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="2"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="2"/>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="32"/>
+      <c r="B81" s="32"/>
+      <c r="C81" s="32"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="2"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="2"/>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="32"/>
+      <c r="B82" s="32"/>
+      <c r="C82" s="32"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="2"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="2"/>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="32"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="32"/>
       <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="2"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="2"/>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="32"/>
+      <c r="B84" s="32"/>
+      <c r="C84" s="32"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="2"/>
-      <c r="B85" s="12"/>
-      <c r="C85" s="2"/>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="32"/>
+      <c r="B85" s="32"/>
+      <c r="C85" s="32"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="2"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="2"/>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="32"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="32"/>
       <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="2"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="2"/>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="32"/>
+      <c r="B87" s="32"/>
+      <c r="C87" s="32"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="32"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-    </row>
-    <row r="89" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="32"/>
+      <c r="B89" s="32"/>
+      <c r="C89" s="32"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="32"/>
+      <c r="B90" s="32"/>
+      <c r="C90" s="32"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-    </row>
-    <row r="91" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="32"/>
+      <c r="B91" s="32"/>
+      <c r="C91" s="32"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="32"/>
+      <c r="B92" s="32"/>
+      <c r="C92" s="32"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-    </row>
-    <row r="93" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="32"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="32"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="32"/>
+      <c r="B94" s="32"/>
+      <c r="C94" s="32"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
+    </row>
+    <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="32"/>
+      <c r="B95" s="32"/>
+      <c r="C95" s="32"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
+    </row>
+    <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="32"/>
+      <c r="B96" s="32"/>
+      <c r="C96" s="32"/>
       <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
+    </row>
+    <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="32"/>
+      <c r="B97" s="32"/>
+      <c r="C97" s="32"/>
       <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="32"/>
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
       <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="32"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="32"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P19" xr:uid="{00000000-0001-0000-0100-000000000000}">
@@ -2112,7 +2336,7 @@
     <mergeCell ref="O1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E73" xr:uid="{117D44D8-0C6C-4370-B730-7F16CE4B6977}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E99" xr:uid="{117D44D8-0C6C-4370-B730-7F16CE4B6977}">
       <formula1>"create, delete, update"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2123,215 +2347,399 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54DD2C41-1A97-4541-9770-3185F7CE6051}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
+        <v>111</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="B3" s="31"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="B4" s="31"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="B5" s="31"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="B6" s="31"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="B7" s="31"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="B8" s="31"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="B9" s="31"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="B10" s="31"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="B11" s="31"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="B12" s="31"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="B13" s="31"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="B14" s="31"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="B15" s="31"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="B16" s="31"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="B17" s="31"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="B18" s="31"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="B19" s="31"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>107</v>
+      </c>
       <c r="B20" s="31"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="12"/>
       <c r="B21" s="31"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C21" s="31"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="12"/>
       <c r="B22" s="31"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C22" s="31"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="12"/>
       <c r="B23" s="31"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C23" s="31"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="8"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="12"/>
       <c r="B24" s="31"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C24" s="31"/>
+      <c r="E24" s="2"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="8"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="31"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C25" s="31"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="8"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
       <c r="B26" s="31"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C26" s="31"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="31"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C27" s="31"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="31"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C28" s="31"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="31"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C29" s="31"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="31"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C30" s="31"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="8"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="31"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H32" s="4"/>
-      <c r="I32" s="8"/>
+      <c r="C31" s="31"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="8"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J32" s="4"/>
+      <c r="K32" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J32 C2:C31" xr:uid="{393645DF-CDE8-4AA9-83CE-9F7519172D5B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L32 D2:D31 E23:E31" xr:uid="{393645DF-CDE8-4AA9-83CE-9F7519172D5B}">
       <formula1>"add, remove-value"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2344,7 +2752,7 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
@@ -2359,197 +2767,197 @@
   <sheetData>
     <row r="1" spans="1:8" s="13" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="25" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="B3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="16" t="s">
         <v>51</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="25" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="25" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="25" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>77</v>
@@ -2558,149 +2966,149 @@
         <v>78</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="13" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E13" s="14" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E14" s="14" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E15" s="14" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E16" s="14" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="5:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E17" s="14" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="5:8" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2708,6 +3116,14 @@
       <c r="F18" s="21"/>
       <c r="G18" s="21"/>
       <c r="H18" s="22"/>
+    </row>
+    <row r="19" spans="5:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2730,6 +3146,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D465A71AD1045A408B389F6BD60EF652" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d1a92ef91123eaf68d47a0f4fab1ea74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="50a37692-28db-4df1-ab56-ea69ffe37abc" xmlns:ns3="3969b2b5-b318-4e89-8b9a-6cb0a1e47a9e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc40742c02336fb0194a9cf27a2126ad" ns2:_="" ns3:_="">
     <xsd:import namespace="50a37692-28db-4df1-ab56-ea69ffe37abc"/>
@@ -2978,15 +3403,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E23D021-FDED-45BB-80BF-0CFEFA186A0F}">
   <ds:schemaRefs>
@@ -2999,6 +3415,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FD9D7CE-5130-460A-B7EB-78C1962584E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1680D75A-B2E7-4B24-ACF1-EFF6BEF34A92}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3015,12 +3439,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FD9D7CE-5130-460A-B7EB-78C1962584E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>